--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130351269</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130351260</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130351269</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130351260</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130351269</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130351260</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130351269</v>
       </c>
       <c r="B3" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130351260</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130351259</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130351269</v>
       </c>
       <c r="B3" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130351260</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130351281</v>
       </c>
       <c r="B5" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130351259</v>
+        <v>130351281</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419346</v>
+        <v>419233</v>
       </c>
       <c r="R2" t="n">
-        <v>7019843</v>
+        <v>7019867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130351269</v>
+        <v>130351285</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419271</v>
+        <v>419449</v>
       </c>
       <c r="R3" t="n">
-        <v>7019829</v>
+        <v>7019640</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130351260</v>
+        <v>130351259</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419398</v>
+        <v>419346</v>
       </c>
       <c r="R4" t="n">
-        <v>7019709</v>
+        <v>7019843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130351281</v>
+        <v>130351260</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419233</v>
+        <v>419398</v>
       </c>
       <c r="R5" t="n">
-        <v>7019867</v>
+        <v>7019709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,6 +1044,11 @@
           <t>2025-12-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1075,6 +1070,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130351269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gärdsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>419271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7019829</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52427-2021 artfynd.xlsx
+++ b/artfynd/A 52427-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351281</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351285</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351259</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,8 +1197,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>